--- a/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -3100,10 +3100,10 @@
         <v>0.421541</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0.999306</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -9464,10 +9464,10 @@
         <v>0.98375</v>
       </c>
       <c r="H210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J210" t="n">
         <v>1</v>
@@ -9811,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="I222" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -10370,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J231" t="n">
         <v>1</v>
@@ -10410,10 +10410,10 @@
         <v>0.335635</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J233" t="n">
         <v>1</v>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J235" t="n">
         <v>1</v>
@@ -10585,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -11015,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J246" t="n">
         <v>1</v>
@@ -11055,10 +11055,10 @@
         <v>0.973564</v>
       </c>
       <c r="H247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J247" t="n">
         <v>1</v>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -11442,10 +11442,10 @@
         <v>0.953773</v>
       </c>
       <c r="H256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J256" t="n">
         <v>1</v>
@@ -11485,10 +11485,10 @@
         <v>0.98683</v>
       </c>
       <c r="H257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J257" t="n">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="I258" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J258" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J259" t="n">
         <v>1</v>
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J262" t="n">
         <v>1</v>
@@ -11789,7 +11789,7 @@
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>0.666667</v>
+        <v>0.6</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -11961,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J268" t="n">
         <v>1</v>
@@ -12133,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -12305,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J276" t="n">
         <v>1</v>
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -13036,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -13165,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J299" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J300" t="n">
         <v>1</v>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -13466,7 +13466,7 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0.666667</v>
+        <v>0.8</v>
       </c>
       <c r="J303" t="n">
         <v>1</v>
@@ -13509,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.666667</v>
+        <v>0.6</v>
       </c>
       <c r="J309" t="n">
         <v>1</v>
@@ -13767,7 +13767,7 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.256886</v>
+        <v>0.160433</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.976464</v>
+        <v>0.989576</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.147201</v>
+        <v>0.092738</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.303227</v>
+        <v>0.232062</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.212848</v>
+        <v>0.149842</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0.176718</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.463632</v>
+        <v>0.543272</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.160809</v>
+        <v>0.120425</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.144288</v>
+        <v>0.122212</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.225941</v>
+        <v>0.147531</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.112165</v>
+        <v>0.063372</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.509715</v>
+        <v>0.582605</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.160904</v>
+        <v>0.148938</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.426154</v>
+        <v>0.295704</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.284528</v>
+        <v>0.223669</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.505467</v>
+        <v>0.6326929999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.138517</v>
+        <v>0.047931</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.238785</v>
+        <v>0.106626</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.153787</v>
+        <v>0.081385</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.137962</v>
+        <v>0.098857</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.119452</v>
+        <v>0.09032800000000001</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.884731</v>
+        <v>0.950766</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.145964</v>
+        <v>0.100037</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.188629</v>
+        <v>0.097536</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.253369</v>
+        <v>0.149753</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.301014</v>
+        <v>0.164678</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.284037</v>
+        <v>0.306789</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.387665</v>
+        <v>0.296453</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.248504</v>
+        <v>0.241525</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.926057</v>
+        <v>0.9718599999999999</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.171122</v>
+        <v>0.094442</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.221484</v>
+        <v>0.135833</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.301135</v>
+        <v>0.200756</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.389417</v>
+        <v>0.294072</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.231063</v>
+        <v>0.161238</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.172851</v>
+        <v>0.107801</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.184069</v>
+        <v>0.139167</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.215799</v>
+        <v>0.164197</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.15519</v>
+        <v>0.113649</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.125647</v>
+        <v>0.075848</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.154972</v>
+        <v>0.101624</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.176928</v>
+        <v>0.083436</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.219084</v>
+        <v>0.110782</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.225322</v>
+        <v>0.150361</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.325973</v>
+        <v>0.270104</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.237783</v>
+        <v>0.167298</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.156487</v>
+        <v>0.09368600000000001</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.289807</v>
+        <v>0.221371</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.238098</v>
+        <v>0.197973</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.585202</v>
+        <v>0.5158</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.494931</v>
+        <v>0.365264</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8955920000000001</v>
+        <v>0.89802</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.233421</v>
+        <v>0.164647</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.323693</v>
+        <v>0.2289</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.651689</v>
+        <v>0.506539</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.08869100000000001</v>
+        <v>0.051564</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.275992</v>
+        <v>0.310245</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.145636</v>
+        <v>0.076284</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.401166</v>
+        <v>0.331171</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>4.3e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.388979</v>
+        <v>0.571939</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9930290000000001</v>
+        <v>0.995955</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.421541</v>
+        <v>0.343879</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.990057</v>
+        <v>0.994969</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.376609</v>
+        <v>0.266854</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.318526</v>
+        <v>0.231033</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.149133</v>
+        <v>0.084317</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.263687</v>
+        <v>0.186758</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.223514</v>
+        <v>0.14652</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.148644</v>
+        <v>0.079981</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.172492</v>
+        <v>0.068688</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.392576</v>
+        <v>0.299792</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.156484</v>
+        <v>0.074341</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.27866</v>
+        <v>0.177582</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.87248</v>
+        <v>0.765997</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.347583</v>
+        <v>0.369342</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.330945</v>
+        <v>0.209928</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.956933</v>
+        <v>0.970279</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>0.979502</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6005239999999999</v>
+        <v>0.411363</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.295225</v>
+        <v>0.217175</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.323504</v>
+        <v>0.224535</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.210446</v>
+        <v>0.187483</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.906735</v>
+        <v>0.935764</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.376142</v>
+        <v>0.310595</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.168972</v>
+        <v>0.085242</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.154754</v>
+        <v>0.113086</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.410351</v>
+        <v>0.403181</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.096251</v>
+        <v>0.06915300000000001</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.134909</v>
+        <v>0.109741</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.979679</v>
+        <v>0.97372</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.053048</v>
+        <v>0.044533</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.12153</v>
+        <v>0.109533</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.201142</v>
+        <v>0.127498</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.269074</v>
+        <v>0.174976</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.20434</v>
+        <v>0.13172</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.323972</v>
+        <v>0.173737</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.483592</v>
+        <v>0.32678</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.245786</v>
+        <v>0.175802</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.59021</v>
+        <v>0.544343</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.98217</v>
+        <v>0.985686</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.298219</v>
+        <v>0.196661</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.999548</v>
+        <v>0.999877</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.999951</v>
+        <v>0.999999</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.703389</v>
+        <v>0.761913</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.22009</v>
+        <v>0.156851</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.143281</v>
+        <v>0.114914</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.610023</v>
+        <v>0.822567</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.342629</v>
+        <v>0.393678</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.233922</v>
+        <v>0.125175</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.768648</v>
+        <v>0.7999230000000001</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.27768</v>
+        <v>0.306993</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.437106</v>
+        <v>0.388447</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.349417</v>
+        <v>0.232745</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.98375</v>
+        <v>0.89374</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.121398</v>
+        <v>0.113842</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.157016</v>
+        <v>0.14468</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.154885</v>
+        <v>0.150265</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.143674</v>
+        <v>0.147613</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.131531</v>
+        <v>0.128404</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0.152498</v>
       </c>
       <c r="F216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.651675</v>
+        <v>0.477172</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.195765</v>
+        <v>0.142584</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0.001996</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.500437</v>
+        <v>0.428198</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.288337</v>
+        <v>0.243836</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.183447</v>
+        <v>0.139826</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.326422</v>
+        <v>0.228793</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9974,10 +9974,10 @@
         <v>0.064883</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0.664129</v>
+        <v>0.435144</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.338147</v>
+        <v>0.240368</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.167275</v>
+        <v>0.147702</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.350526</v>
+        <v>0.189095</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.124797</v>
+        <v>0.12904</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.350971</v>
+        <v>0.253969</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.131963</v>
+        <v>0.133959</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.103162</v>
+        <v>0.13637</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.226411</v>
+        <v>0.141588</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.805406</v>
+        <v>0.877898</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.335635</v>
+        <v>0.452478</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.999146</v>
+        <v>0.999789</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.21576</v>
+        <v>0.250786</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.634944</v>
+        <v>0.654126</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.130751</v>
+        <v>0.135611</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.129323</v>
+        <v>0.119152</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.138146</v>
+        <v>0.107463</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.102282</v>
+        <v>0.115563</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.11973</v>
+        <v>0.09947300000000001</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.141493</v>
+        <v>0.159971</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.07341399999999999</v>
+        <v>0.08637400000000001</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.231862</v>
+        <v>0.218351</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.200889</v>
+        <v>0.196314</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>0.000607</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.461761</v>
+        <v>0.58436</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.879337</v>
+        <v>0.961283</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.973564</v>
+        <v>0.994568</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.562304</v>
+        <v>0.614832</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.996158</v>
+        <v>0.999098</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.248864</v>
+        <v>0.156828</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.133832</v>
+        <v>0.164838</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.602469</v>
+        <v>0.593926</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.129017</v>
+        <v>0.073653</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.255083</v>
+        <v>0.248016</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>0.545187</v>
+        <v>0.557069</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.953773</v>
+        <v>0.971957</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.98683</v>
+        <v>0.991401</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.868211</v>
+        <v>0.940404</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.921102</v>
+        <v>0.973417</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.154991</v>
+        <v>0.125978</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.8257370000000001</v>
+        <v>0.835443</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.541591</v>
+        <v>0.611677</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.198905</v>
+        <v>0.102015</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.974314</v>
+        <v>0.988744</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.121869</v>
+        <v>0.134588</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.102339</v>
+        <v>0.103899</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.969724</v>
+        <v>0.972089</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.964668</v>
+        <v>0.988842</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.152205</v>
+        <v>0.145036</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.228803</v>
+        <v>0.183929</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.125847</v>
+        <v>0.08795600000000001</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.289048</v>
+        <v>0.347747</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12167,10 +12167,10 @@
         <v>0.886833</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.484733</v>
+        <v>0.6235849999999999</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.603174</v>
+        <v>0.7058759999999999</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.395432</v>
+        <v>0.385627</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.6237009999999999</v>
+        <v>0.702913</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.259685</v>
+        <v>0.227764</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.237019</v>
+        <v>0.330539</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.186853</v>
+        <v>0.143496</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.138479</v>
+        <v>0.112202</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.244717</v>
+        <v>0.213477</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.10919</v>
+        <v>0.102272</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.127735</v>
+        <v>0.108066</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.137424</v>
+        <v>0.109036</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.349892</v>
+        <v>0.197117</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.490054</v>
+        <v>0.339938</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.896338</v>
+        <v>0.76059</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.320602</v>
+        <v>0.229414</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.187827</v>
+        <v>0.194579</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.208037</v>
+        <v>0.246409</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.257657</v>
+        <v>0.236302</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.328689</v>
+        <v>0.205996</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.318213</v>
+        <v>0.25626</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.080049</v>
+        <v>0.07672</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.106839</v>
+        <v>0.127634</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.997443</v>
+        <v>0.999397</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0.061195</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.463533</v>
+        <v>0.6301</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.240493</v>
+        <v>0.268379</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13285,10 +13285,10 @@
         <v>0.146906</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.412267</v>
+        <v>0.570758</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.339537</v>
+        <v>0.288975</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.134482</v>
+        <v>0.118315</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.290084</v>
+        <v>0.223585</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.8338</v>
+        <v>0.970282</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.976465</v>
+        <v>0.989859</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.180651</v>
+        <v>0.110567</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.265746</v>
+        <v>0.273066</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.239573</v>
+        <v>0.170578</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.218847</v>
+        <v>0.178859</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.598697</v>
+        <v>0.828067</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.101237</v>
+        <v>0.067136</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.24774</v>
+        <v>0.127662</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.156665</v>
+        <v>0.108117</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.259974</v>
+        <v>0.277209</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.080412</v>
+        <v>0.04351</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.141403</v>
+        <v>0.098257</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.197797</v>
+        <v>0.151076</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.097634</v>
+        <v>0.047138</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14102,10 +14102,10 @@
         <v>0.010059</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.499814</v>
+        <v>0.718661</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.427784</v>
+        <v>0.468215</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.84836</v>
+        <v>0.926689</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.133509</v>
+        <v>0.062222</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.270224</v>
+        <v>0.074924</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.220863</v>
+        <v>0.09180199999999999</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.149894</v>
+        <v>0.107193</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.108048</v>
+        <v>0.024151</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.272424</v>
+        <v>0.13713</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.315026</v>
+        <v>0.175711</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.715214</v>
+        <v>0.850464</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.223246</v>
+        <v>0.102367</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.146002</v>
+        <v>0.065792</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.968788</v>
+        <v>0.9878980000000001</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.111415</v>
+        <v>0.040132</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.990461</v>
+        <v>0.997448</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.256226</v>
+        <v>0.294553</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.231504</v>
+        <v>0.124742</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.436642</v>
+        <v>0.152259</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.118263</v>
+        <v>0.032073</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.242592</v>
+        <v>0.08883000000000001</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.114373</v>
+        <v>0.025426</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.300172</v>
+        <v>0.190088</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.169489</v>
+        <v>0.07653799999999999</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.126051</v>
+        <v>0.032717</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.143461</v>
+        <v>0.050517</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.115502</v>
+        <v>0.021217</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.253738</v>
+        <v>0.120609</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.229252</v>
+        <v>0.08742900000000001</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.375379</v>
+        <v>0.116597</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.474612</v>
+        <v>0.337251</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.5445719999999999</v>
+        <v>0.7129760000000001</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.581008</v>
+        <v>0.854626</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15521,10 +15521,10 @@
         <v>0.032669</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.5274990000000001</v>
+        <v>0.453118</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.190346</v>
+        <v>0.089126</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.12793</v>
+        <v>0.074694</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.192491</v>
+        <v>0.063624</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.090686</v>
+        <v>0.037008</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.071995</v>
+        <v>0.022722</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.112771</v>
+        <v>0.052997</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.311262</v>
+        <v>0.193179</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.070855</v>
+        <v>0.020316</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.604043</v>
+        <v>0.565856</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.399647</v>
+        <v>0.357943</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.988057</v>
+        <v>0.998587</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.130644</v>
+        <v>0.056979</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.958672</v>
+        <v>0.993469</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.163465</v>
+        <v>0.09205000000000001</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.342436</v>
+        <v>0.23821</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16209,10 +16209,10 @@
         <v>0.000342</v>
       </c>
       <c r="F367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.629961</v>
+        <v>0.420133</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.24748</v>
+        <v>0.146916</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.300948</v>
+        <v>0.182959</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.219148</v>
+        <v>0.14416</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.903138</v>
+        <v>0.968206</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.124985</v>
+        <v>0.05778</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.1653</v>
+        <v>0.133752</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.277279</v>
+        <v>0.217131</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.204881</v>
+        <v>0.09675499999999999</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.108819</v>
+        <v>0.065833</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.209152</v>
+        <v>0.110372</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.277427</v>
+        <v>0.19245</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.255416</v>
+        <v>0.160011</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.531502</v>
+        <v>0.686759</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.340363</v>
+        <v>0.179976</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.523157</v>
+        <v>0.733287</v>
       </c>
       <c r="H382" t="n">
         <v>1</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.106427</v>
+        <v>0.047649</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.150124</v>
+        <v>0.085647</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.075321</v>
+        <v>0.024051</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.102912</v>
+        <v>0.027861</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.285837</v>
+        <v>0.215059</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.324619</v>
+        <v>0.173011</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.110178</v>
+        <v>0.067339</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.196797</v>
+        <v>0.08221100000000001</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.178375</v>
+        <v>0.138205</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17284,10 +17284,10 @@
         <v>2e-06</v>
       </c>
       <c r="F392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.5833120000000001</v>
+        <v>0.393564</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.7630710000000001</v>
+        <v>0.864976</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.230668</v>
+        <v>0.112204</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.748259</v>
+        <v>0.708569</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.307261</v>
+        <v>0.156597</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17499,10 +17499,10 @@
         <v>0.121974</v>
       </c>
       <c r="F397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.407404</v>
+        <v>0.513025</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.318782</v>
+        <v>0.227563</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.178559</v>
+        <v>0.108687</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.16894</v>
+        <v>0.07680099999999999</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.355181</v>
+        <v>0.187743</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.180034</v>
+        <v>0.07807699999999999</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.9784310000000001</v>
+        <v>0.986376</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.147704</v>
+        <v>0.067116</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.181498</v>
+        <v>0.073476</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.207395</v>
+        <v>0.099837</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.689041</v>
+        <v>0.783868</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.9838710000000001</v>
+        <v>0.992949</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0.860496</v>
+        <v>0.905999</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.156724</v>
+        <v>0.069051</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.91744</v>
+        <v>0.9774119999999999</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.9171319999999999</v>
+        <v>0.988455</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.100636</v>
+        <v>0.070701</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.935889</v>
+        <v>0.962874</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
